--- a/forms/trg/Formulir_TRG_periodontal.xlsx
+++ b/forms/trg/Formulir_TRG_periodontal.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B22)</f>
+        <f>COUNTA(Anggota!B5:B23)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F22)</f>
+        <f>COUNTA(Anggota!F5:F23)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,19 +913,15 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Surijana Mappangara</t>
+          <t>Sri Oktawati</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
@@ -933,13 +929,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4215-6412</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="n"/>
+          <t>0000-0002-9212-6641</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6029544</t>
+        </is>
+      </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57204103430</t>
+          <t>57200225135</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Juni Jekti Nugroho</t>
+          <t>Surijana Mappangara</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -972,9 +972,17 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-4215-6412</t>
+        </is>
+      </c>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>57204103430</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -987,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Nurlindah Hamrun</t>
+          <t>Juni Jekti Nugroho</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1005,17 +1013,9 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-6000-7480</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>57204107318</t>
-        </is>
-      </c>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Yasir Dilshad Siddiqui</t>
+          <t>Nurlindah Hamrun</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Jouf University KSA</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -1048,13 +1048,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0395-0098</t>
+          <t>0000-0001-6000-7480</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57207764715</t>
+          <t>57204107318</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Joyce Srinovita</t>
+          <t>Yasir Dilshad Siddiqui</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Jouf University KSA</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
@@ -1087,9 +1087,17 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0395-0098</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>57207764715</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1102,12 +1110,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Yoko Fitriansyah</t>
+          <t>Joyce Srinovita</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1133,10 +1141,26 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Yoko Fitriansyah</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>The Tissue Engineering for Periodontal Treatment Research Group explores innovative bone graft solutions using dentin from extracted teeth. By developing autograft methods that meet gold standards, the group aims to provide affordable, effective periodontal treatment while minimizing surgical risks and utilizing medical waste sustainably.</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1144,7 +1168,11 @@
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1333,15 +1361,32 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="12" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
